--- a/survey_templates/024_child_marriage_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/024_child_marriage_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'non-binary',_'value':_'nonbinary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Non-binary', 'value': 'nonbinary'}</t>
+          <t>Non-binary</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'prefer_not_to_say',_'value':_'skip'}</t>
+          <t>prefer_not_to_say</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Prefer not to say', 'value': 'skip'}</t>
+          <t>Prefer not to say</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'under_18',_'value':_'minor'}</t>
+          <t>under_18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Under 18', 'value': 'minor'}</t>
+          <t>Under 18</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'18_to_24',_'value':_1824}</t>
+          <t>18_to_24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '18 to 24', 'value': 1824}</t>
+          <t>18 to 24</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'25_to_34',_'value':_2534}</t>
+          <t>25_to_34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '25 to 34', 'value': 2534}</t>
+          <t>25 to 34</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'35_to_44',_'value':_3544}</t>
+          <t>35_to_44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '35 to 44', 'value': 3544}</t>
+          <t>35 to 44</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'45_and_older',_'value':_'45plus'}</t>
+          <t>45_and_older</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '45 and Older', 'value': '45plus'}</t>
+          <t>45 and Older</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_i_am_aware',_'value':_true}</t>
+          <t>yes_-_i_am_aware</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - I am aware', 'value': True}</t>
+          <t>Yes - I am aware</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_i_am_not_aware',_'value':_false}</t>
+          <t>no_-_i_am_not_aware</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No - I am not aware', 'value': False}</t>
+          <t>No - I am not aware</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'18_to_21',_'value':_1821}</t>
+          <t>18_to_21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '18 to 21', 'value': 1821}</t>
+          <t>18 to 21</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'22_to_25',_'value':_2225}</t>
+          <t>22_to_25</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '22 to 25', 'value': 2225}</t>
+          <t>22 to 25</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'26_to_30',_'value':_2630}</t>
+          <t>26_to_30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '26 to 30', 'value': 2630}</t>
+          <t>26 to 30</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'over_30',_'value':_'30plus'}</t>
+          <t>over_30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Over 30', 'value': '30plus'}</t>
+          <t>Over 30</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree',_'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree', 'value': 'strongly_agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'agree',_'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Agree', 'value': 'agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'disagree',_'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree', 'value': 'disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Unsure', 'value': 'unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_active_programs',_'value':_true}</t>
+          <t>yes_-_active_programs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Active Programs', 'value': True}</t>
+          <t>Yes - Active Programs</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_none_observed',_'value':_false}</t>
+          <t>no_-_none_observed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'No - None Observed', 'value': False}</t>
+          <t>No - None Observed</t>
         </is>
       </c>
     </row>
